--- a/docs/exports/Corporate_Finance_Decision_Lab.xlsx
+++ b/docs/exports/Corporate_Finance_Decision_Lab.xlsx
@@ -1723,7 +1723,7 @@
         <x:v>WACC</x:v>
       </x:c>
       <x:c r="D12" s="42" t="n">
-        <x:f>IF(AND(ISNUMBER($D$4),$D$4=INT($D$4),$D$4&gt;=1,$D$4&lt;=9),IF(AND(COUNTBLANK(INDEX($D$23:$L$23,1,$D$4))=0,ISNUMBER(INDEX($D$23:$L$23,1,$D$4)),INDEX($D$23:$L$23,1,$D$4)&gt;0,INDEX($D$23:$L$23,1,$D$4)&lt;=0.5,INDEX($D$23:$L$23,1,$D$4)-$D$11&gt;=0.0001),INDEX($D$23:$L$23,1,$D$4),NA()),NA())</x:f>
+        <x:f>IF(AND(ISNUMBER($D$4),$D$4=INT($D$4),$D$4&gt;=1,$D$4&lt;=9),IF(AND(COUNTBLANK(INDEX($D$23:$L$23,1,$D$4))=0,ISNUMBER(INDEX($D$23:$L$23,1,$D$4)),INDEX($D$23:$L$23,1,$D$4)&gt;0,INDEX($D$23:$L$23,1,$D$4)&lt;=0.5,INDEX($D$23:$L$23,1,$D$4)-$D$11&gt;=0.0001-1.7763568394002505E-15*MAX(ABS(INDEX($D$23:$L$23,1,$D$4)),ABS($D$11),0.0001)),INDEX($D$23:$L$23,1,$D$4),NA()),NA())</x:f>
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="E12" s="2"/>
